--- a/tests/workbooktests/workbooks/test_blackformula.xlsx
+++ b/tests/workbooktests/workbooks/test_blackformula.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9408C4C9-6617-41FA-AD76-2BFECB358B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FE99D9-E931-4807-80BF-2C2800E279F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3890" yWindow="-20000" windowWidth="23040" windowHeight="16910" activeTab="1" xr2:uid="{E3B161FE-8CB9-4540-8E3F-BFF22FA5846A}"/>
+    <workbookView xWindow="3645" yWindow="-19185" windowWidth="30690" windowHeight="16530" xr2:uid="{E3B161FE-8CB9-4540-8E3F-BFF22FA5846A}"/>
   </bookViews>
   <sheets>
     <sheet name="Black_Bachlier" sheetId="1" r:id="rId1"/>
@@ -159,9 +159,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.00000000"/>
-    <numFmt numFmtId="171" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.00000000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -202,13 +202,13 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -645,39 +645,39 @@
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" cm="1">
-        <f t="array" ref="B10">_xll.qlBlackFormula(B2,B3,B4,B7)</f>
-        <v>14.031620480133384</v>
-      </c>
-      <c r="C10" cm="1">
-        <f t="array" ref="C10">_xll.qlBlackFormula(C2,C3,C4,C7,C8,C9)</f>
-        <v>13.996541428933039</v>
+      <c r="B10" t="e" cm="1">
+        <f t="array" aca="1" ref="B10" ca="1">_xll.qlBlackFormula(B2,B3,B4,B7)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C10" t="e" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_xll.qlBlackFormula(C2,C3,C4,C7,C8,C9)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" cm="1">
-        <f t="array" ref="B11">_xll.qlBlackFormulaImpliedStdDev(B2,B3,B4,B10)</f>
-        <v>0.35355339059327262</v>
-      </c>
-      <c r="C11" cm="1">
-        <f t="array" ref="C11">_xll.qlBlackFormulaImpliedStdDev(C2,C3,C4,C10,C8,C9,0.3,0.001,10)</f>
-        <v>0.35355339002122016</v>
+      <c r="B11" t="e" cm="1">
+        <f t="array" aca="1" ref="B11" ca="1">_xll.qlBlackFormulaImpliedStdDev(B2,B3,B4,B10)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C11" t="e" cm="1">
+        <f t="array" aca="1" ref="C11" ca="1">_xll.qlBlackFormulaImpliedStdDev(C2,C3,C4,C10,C8,C9,0.3,0.001,10)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" cm="1">
-        <f t="array" ref="B12">_xll.qlBlackFormulaImpliedStdDevLiRS(B2,B3,B4,B10)</f>
-        <v>0.35355339059327362</v>
-      </c>
-      <c r="C12" s="4" cm="1">
-        <f t="array" ref="C12">_xll.qlBlackFormulaImpliedStdDevLiRS(C2,C3,C4,C10,C8,C9,0.3,0.8,0.001,10)</f>
-        <v>0.35356686629940487</v>
+      <c r="B12" t="e" cm="1">
+        <f t="array" aca="1" ref="B12" ca="1">_xll.qlBlackFormulaImpliedStdDevLiRS(B2,B3,B4,B10)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C12" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="C12" ca="1">_xll.qlBlackFormulaImpliedStdDevLiRS(C2,C3,C4,C10,C8,C9,0.3,0.8,0.001,10)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -760,37 +760,37 @@
       <c r="A22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B22" cm="1">
-        <f t="array" ref="B22">_xll.qlBachelierBlackFormula(B15,B16,B17,B20)</f>
-        <v>6.3031897859580308</v>
-      </c>
-      <c r="C22" cm="1">
-        <f t="array" ref="C22">_xll.qlBachelierBlackFormula(C15,C16,C17,C20,C21,#REF!)</f>
-        <v>14.104739588693908</v>
+      <c r="B22" t="e" cm="1">
+        <f t="array" aca="1" ref="B22" ca="1">_xll.qlBachelierBlackFormula(B15,B16,B17,B20)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C22" t="e" cm="1">
+        <f t="array" aca="1" ref="C22" ca="1">_xll.qlBachelierBlackFormula(C15,C16,C17,C20,C21,B22)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="5" cm="1">
-        <f t="array" ref="B23">_xll.qlBachelierBlackFormulaImpliedVol(B15,B16,B17,B18,B22)</f>
-        <v>24.999999999999996</v>
-      </c>
-      <c r="C23" s="5" cm="1">
-        <f t="array" ref="C23">_xll.qlBachelierBlackFormulaImpliedVol(C15,C16,C17,C18,C22,C21)</f>
-        <v>24.999999999999996</v>
+      <c r="B23" s="5" t="e" cm="1">
+        <f t="array" aca="1" ref="B23" ca="1">_xll.qlBachelierBlackFormulaImpliedVol(B15,B16,B17,B18,B22)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C23" s="5" t="e" cm="1">
+        <f t="array" aca="1" ref="C23" ca="1">_xll.qlBachelierBlackFormulaImpliedVol(C15,C16,C17,C18,C22,C21)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
-      <c r="B24" s="5" cm="1">
-        <f t="array" ref="B24">_xll.qlBachelierBlackFormulaImpliedVolChoi(B15,B16,B17,B18,B22)</f>
-        <v>24.999999999999051</v>
-      </c>
-      <c r="C24" s="5" cm="1">
-        <f t="array" ref="C24">_xll.qlBachelierBlackFormulaImpliedVolChoi(C15,C16,C17,C18,C22,C21)</f>
-        <v>24.999999999999975</v>
+      <c r="B24" s="5" t="e" cm="1">
+        <f t="array" aca="1" ref="B24" ca="1">_xll.qlBachelierBlackFormulaImpliedVolChoi(B15,B16,B17,B18,B22)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C24" s="5" t="e" cm="1">
+        <f t="array" aca="1" ref="C24" ca="1">_xll.qlBachelierBlackFormulaImpliedVolChoi(C15,C16,C17,C18,C22,C21)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -844,21 +844,21 @@
       <c r="D3">
         <v>50</v>
       </c>
-      <c r="E3" s="5" cm="1">
-        <f t="array" ref="E3">_xll.qlBlackDeltaCalculatorDeltaFromStrike($B$11,D3)</f>
-        <v>0.98371291535131311</v>
-      </c>
-      <c r="F3" s="5" cm="1">
-        <f t="array" ref="F3">_xll.qlBlackDeltaCalculatorDeltaFromStrike($B$12,D3)</f>
-        <v>-1.6287084648686834E-2</v>
-      </c>
-      <c r="G3" s="7" cm="1">
-        <f t="array" ref="G3">_xll.qlBlackDeltaCalculatorStrikeFromDelta($B$11,E3)</f>
-        <v>50.000000041662304</v>
-      </c>
-      <c r="H3" s="7" cm="1">
-        <f t="array" ref="H3">_xll.qlBlackDeltaCalculatorStrikeFromDelta($B$12,F3)</f>
-        <v>50.000000041662275</v>
+      <c r="E3" s="5" t="e" cm="1">
+        <f t="array" aca="1" ref="E3" ca="1">_xll.qlBlackDeltaCalculatorDeltaFromStrike($B$11,D3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F3" s="5" t="e" cm="1">
+        <f t="array" aca="1" ref="F3" ca="1">_xll.qlBlackDeltaCalculatorDeltaFromStrike($B$12,D3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G3" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="G3" ca="1">_xll.qlBlackDeltaCalculatorStrikeFromDelta($B$11,E3)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H3" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="H3" ca="1">_xll.qlBlackDeltaCalculatorStrikeFromDelta($B$12,F3)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -871,21 +871,21 @@
       <c r="D4">
         <v>75</v>
       </c>
-      <c r="E4" s="5" cm="1">
-        <f t="array" ref="E4">_xll.qlBlackDeltaCalculatorDeltaFromStrike($B$11,D4)</f>
-        <v>0.83902642694485707</v>
-      </c>
-      <c r="F4" s="5" cm="1">
-        <f t="array" ref="F4">_xll.qlBlackDeltaCalculatorDeltaFromStrike($B$12,D4)</f>
-        <v>-0.16097357305514298</v>
-      </c>
-      <c r="G4" s="7" cm="1">
-        <f t="array" ref="G4">_xll.qlBlackDeltaCalculatorStrikeFromDelta($B$11,E4)</f>
-        <v>74.999999977985325</v>
-      </c>
-      <c r="H4" s="7" cm="1">
-        <f t="array" ref="H4">_xll.qlBlackDeltaCalculatorStrikeFromDelta($B$12,F4)</f>
-        <v>74.999999977985382</v>
+      <c r="E4" s="5" t="e" cm="1">
+        <f t="array" aca="1" ref="E4" ca="1">_xll.qlBlackDeltaCalculatorDeltaFromStrike($B$11,D4)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F4" s="5" t="e" cm="1">
+        <f t="array" aca="1" ref="F4" ca="1">_xll.qlBlackDeltaCalculatorDeltaFromStrike($B$12,D4)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G4" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="G4" ca="1">_xll.qlBlackDeltaCalculatorStrikeFromDelta($B$11,E4)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H4" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="H4" ca="1">_xll.qlBlackDeltaCalculatorStrikeFromDelta($B$12,F4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -898,21 +898,21 @@
       <c r="D5">
         <v>100</v>
       </c>
-      <c r="E5" s="5" cm="1">
-        <f t="array" ref="E5">_xll.qlBlackDeltaCalculatorDeltaFromStrike($B$11,D5)</f>
-        <v>0.57015810240066689</v>
-      </c>
-      <c r="F5" s="5" cm="1">
-        <f t="array" ref="F5">_xll.qlBlackDeltaCalculatorDeltaFromStrike($B$12,D5)</f>
-        <v>-0.42984189759933311</v>
-      </c>
-      <c r="G5" s="7" cm="1">
-        <f t="array" ref="G5">_xll.qlBlackDeltaCalculatorStrikeFromDelta($B$11,E5)</f>
-        <v>100.00000000294807</v>
-      </c>
-      <c r="H5" s="7" cm="1">
-        <f t="array" ref="H5">_xll.qlBlackDeltaCalculatorStrikeFromDelta($B$12,F5)</f>
-        <v>100.00000000294807</v>
+      <c r="E5" s="5" t="e" cm="1">
+        <f t="array" aca="1" ref="E5" ca="1">_xll.qlBlackDeltaCalculatorDeltaFromStrike($B$11,D5)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F5" s="5" t="e" cm="1">
+        <f t="array" aca="1" ref="F5" ca="1">_xll.qlBlackDeltaCalculatorDeltaFromStrike($B$12,D5)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G5" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="G5" ca="1">_xll.qlBlackDeltaCalculatorStrikeFromDelta($B$11,E5)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H5" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="H5" ca="1">_xll.qlBlackDeltaCalculatorStrikeFromDelta($B$12,F5)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -927,13 +927,13 @@
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
-      <c r="G6" s="7" cm="1">
-        <f t="array" ref="G6">_xll.qlBlackDeltaCalculatorAtmStrike($B$11,$B$14)</f>
-        <v>106.44944589178596</v>
-      </c>
-      <c r="H6" s="7" cm="1">
-        <f t="array" ref="H6">_xll.qlBlackDeltaCalculatorAtmStrike($B$12,$B$14)</f>
-        <v>106.44944589178596</v>
+      <c r="G6" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="G6" ca="1">_xll.qlBlackDeltaCalculatorAtmStrike($B$11,$B$14)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H6" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="H6" ca="1">_xll.qlBlackDeltaCalculatorAtmStrike($B$12,$B$14)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -946,21 +946,21 @@
       <c r="D7">
         <v>125</v>
       </c>
-      <c r="E7" s="5" cm="1">
-        <f t="array" ref="E7">_xll.qlBlackDeltaCalculatorDeltaFromStrike($B$11,D7)</f>
-        <v>0.32478178224178167</v>
-      </c>
-      <c r="F7" s="5" cm="1">
-        <f t="array" ref="F7">_xll.qlBlackDeltaCalculatorDeltaFromStrike($B$12,D7)</f>
-        <v>-0.67521821775821833</v>
-      </c>
-      <c r="G7" s="7" cm="1">
-        <f t="array" ref="G7">_xll.qlBlackDeltaCalculatorStrikeFromDelta($B$11,E7)</f>
-        <v>125.00000001051117</v>
-      </c>
-      <c r="H7" s="7" cm="1">
-        <f t="array" ref="H7">_xll.qlBlackDeltaCalculatorStrikeFromDelta($B$12,F7)</f>
-        <v>125.00000001051117</v>
+      <c r="E7" s="5" t="e" cm="1">
+        <f t="array" aca="1" ref="E7" ca="1">_xll.qlBlackDeltaCalculatorDeltaFromStrike($B$11,D7)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F7" s="5" t="e" cm="1">
+        <f t="array" aca="1" ref="F7" ca="1">_xll.qlBlackDeltaCalculatorDeltaFromStrike($B$12,D7)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G7" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="G7" ca="1">_xll.qlBlackDeltaCalculatorStrikeFromDelta($B$11,E7)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H7" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="H7" ca="1">_xll.qlBlackDeltaCalculatorStrikeFromDelta($B$12,F7)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -973,21 +973,21 @@
       <c r="D8">
         <v>150</v>
       </c>
-      <c r="E8" s="5" cm="1">
-        <f t="array" ref="E8">_xll.qlBlackDeltaCalculatorDeltaFromStrike($B$11,D8)</f>
-        <v>0.16601033275327931</v>
-      </c>
-      <c r="F8" s="5" cm="1">
-        <f t="array" ref="F8">_xll.qlBlackDeltaCalculatorDeltaFromStrike($B$12,D8)</f>
-        <v>-0.83398966724672063</v>
-      </c>
-      <c r="G8" s="7" cm="1">
-        <f t="array" ref="G8">_xll.qlBlackDeltaCalculatorStrikeFromDelta($B$11,E8)</f>
-        <v>150.00000003113115</v>
-      </c>
-      <c r="H8" s="7" cm="1">
-        <f t="array" ref="H8">_xll.qlBlackDeltaCalculatorStrikeFromDelta($B$12,F8)</f>
-        <v>150.00000003113109</v>
+      <c r="E8" s="5" t="e" cm="1">
+        <f t="array" aca="1" ref="E8" ca="1">_xll.qlBlackDeltaCalculatorDeltaFromStrike($B$11,D8)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F8" s="5" t="e" cm="1">
+        <f t="array" aca="1" ref="F8" ca="1">_xll.qlBlackDeltaCalculatorDeltaFromStrike($B$12,D8)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G8" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="G8" ca="1">_xll.qlBlackDeltaCalculatorStrikeFromDelta($B$11,E8)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H8" s="7" t="e" cm="1">
+        <f t="array" aca="1" ref="H8" ca="1">_xll.qlBlackDeltaCalculatorStrikeFromDelta($B$12,F8)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -1011,18 +1011,18 @@
       <c r="A11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="2" t="str" cm="1">
-        <f t="array" ref="B11">_xll.qlBlackDeltaCalculator(B2,B4,B5,B6,B7,B10)</f>
-        <v>⚡[test_blackformula.xlsx]BlackDeltaCalculator!R11C2BlackDeltaCalculator,A</v>
+      <c r="B11" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B11" ca="1">_xll.qlBlackDeltaCalculator(B2,B4,B5,B6,B7,B10)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2" t="str" cm="1">
-        <f t="array" ref="B12">_xll.qlBlackDeltaCalculator(B3,B4,B5,B6,B7,B10)</f>
-        <v>⚡[test_blackformula.xlsx]BlackDeltaCalculator!R12C2BlackDeltaCalculator,A</v>
+      <c r="B12" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="B12" ca="1">_xll.qlBlackDeltaCalculator(B3,B4,B5,B6,B7,B10)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
